--- a/WebApi/wwwroot/uploads/reports/1.xlsx
+++ b/WebApi/wwwroot/uploads/reports/1.xlsx
@@ -6,8 +6,8 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="الملخص" sheetId="1" r:id="rId2"/>
-    <x:sheet name="التفاصيل الشهرية" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Summary" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Monthly Breakdown" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -17,52 +17,55 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>الملخص المالي</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-01  →  2026-06-30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>إجمالي الدخل</x:t>
-  </x:si>
-  <x:si>
-    <x:t>إجمالي المصروفات</x:t>
-  </x:si>
-  <x:si>
-    <x:t>صافي الرصيد</x:t>
-  </x:si>
-  <x:si>
-    <x:t>إجمالي المعاملات</x:t>
+    <x:t>Financial Summary</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-01  →  2026-07-31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total Income</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total Expenses</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Net Balance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total Transactions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Active Months</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>الأشهر النشطة</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>التوزيع الشهري</x:t>
-  </x:si>
-  <x:si>
-    <x:t>الشهر</x:t>
-  </x:si>
-  <x:si>
-    <x:t>الدخل</x:t>
-  </x:si>
-  <x:si>
-    <x:t>المصروفات</x:t>
-  </x:si>
-  <x:si>
-    <x:t>عدد المعاملات</x:t>
-  </x:si>
-  <x:si>
-    <x:t>يونيو 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>الإجمالي</x:t>
+    <x:t>Monthly Breakdown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Month</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Income</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Expenses</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transactions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>June 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>July 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -160,7 +163,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -175,6 +178,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1E3A8A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF6FF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -219,7 +227,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="14">
+  <x:cellStyleXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -256,14 +264,23 @@
     <x:xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -312,11 +329,23 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -637,7 +666,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="4">
-        <x:v>103</x:v>
+        <x:v>1423</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -647,7 +676,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="5">
-        <x:v>5.55</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C5" s="5"/>
       <x:c r="D5" s="5"/>
@@ -657,7 +686,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="4">
-        <x:v>97.45</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -705,7 +734,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E5"/>
+  <x:dimension ref="A1:E6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22.710625" style="0" customWidth="1"/>
@@ -739,33 +768,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="10">
-        <x:v>103</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="C4" s="10">
-        <x:v>5.55</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="11">
-        <x:v>97.45</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="E4" s="9">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:5">
+    <x:row r="5" spans="1:5" ht="18" customHeight="1">
       <x:c r="A5" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="13">
-        <x:v>103</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="C5" s="13">
-        <x:v>5.55</x:v>
-      </x:c>
-      <x:c r="D5" s="13">
-        <x:v>97.45</x:v>
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D5" s="14">
+        <x:v>507</x:v>
       </x:c>
       <x:c r="E5" s="12">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="16">
+        <x:v>1423</x:v>
+      </x:c>
+      <x:c r="C6" s="16">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D6" s="16">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="E6" s="15">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
